--- a/satisfaction_surveys/026_vinegar_usage_survey--satisfaction_surveys.xlsx
+++ b/satisfaction_surveys/026_vinegar_usage_survey--satisfaction_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="41" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="37" customWidth="1" min="3" max="3"/>
     <col width="50" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -846,12 +846,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>satisfaction_likely_to_recommend</t>
+          <t>satisfaction_likely_to_recommend_2</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Likely to Recommend</t>
+          <t>Satisfaction Likely To Recommend 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Likely to Recommend</t>
+          <t>Satisfaction Likley To Recommend</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -943,7 +943,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Suggest Improvements</t>
+          <t>Satisfaction Suggest Improvements 1</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -966,7 +966,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Suggest Improvements</t>
+          <t>Satisfaction Suggest Improvements 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -1007,12 +1007,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied</t>
+          <t>satisfaction_very_satisfied_2</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Satisfaction Very Satisfied 2</t>
         </is>
       </c>
       <c r="D25" t="inlineStr"/>
@@ -1030,12 +1030,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied</t>
+          <t>satisfaction_very_satisfied_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Satisfaction Very Satisfied 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1053,12 +1053,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied</t>
+          <t>satisfaction_very_satisfied_4</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Satisfaction Very Satisfied 4</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied</t>
+          <t>satisfaction_very_satisfied_5</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Very Satisfied</t>
+          <t>Satisfaction Very Satisfied 5</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1128,7 +1128,7 @@
   <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="43" customWidth="1" min="1" max="1"/>
+    <col width="44" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="24" customWidth="1" min="3" max="3"/>
   </cols>
@@ -1595,7 +1595,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>satisfaction_likely_to_recommend_choices</t>
+          <t>satisfaction_likely_to_recommend_2_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1612,7 +1612,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>satisfaction_likely_to_recommend_choices</t>
+          <t>satisfaction_likely_to_recommend_2_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1731,7 +1731,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied_choices</t>
+          <t>satisfaction_very_satisfied_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1748,7 +1748,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied_choices</t>
+          <t>satisfaction_very_satisfied_2_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1765,7 +1765,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied_choices</t>
+          <t>satisfaction_very_satisfied_3_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -1782,7 +1782,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied_choices</t>
+          <t>satisfaction_very_satisfied_3_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -1799,7 +1799,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied_choices</t>
+          <t>satisfaction_very_satisfied_4_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -1816,7 +1816,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied_choices</t>
+          <t>satisfaction_very_satisfied_4_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -1833,7 +1833,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied_choices</t>
+          <t>satisfaction_very_satisfied_5_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -1850,7 +1850,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>satisfaction_very_satisfied_choices</t>
+          <t>satisfaction_very_satisfied_5_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
